--- a/Excel/EquipStrengthFeeConfig.xlsx
+++ b/Excel/EquipStrengthFeeConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -1158,7 +1163,6 @@
         <v>2</v>
       </c>
       <c r="D7" s="2">
-        <f>E6+1</f>
         <v>31</v>
       </c>
       <c r="E7" s="2">
@@ -1182,13 +1186,27 @@
     <row r="8" customFormat="1" ht="18" customHeight="1" spans="1:9 16370:16371">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
+      <c r="C8" s="2">
+        <v>3</v>
+      </c>
+      <c r="D8" s="2">
+        <v>31</v>
+      </c>
+      <c r="E8" s="2">
+        <v>90</v>
+      </c>
+      <c r="F8" s="2">
+        <v>150000</v>
+      </c>
+      <c r="G8" s="2">
+        <v>2</v>
+      </c>
+      <c r="H8" s="2">
+        <v>80</v>
+      </c>
+      <c r="I8" s="2">
+        <v>2</v>
+      </c>
       <c r="XEP8" s="2"/>
       <c r="XEQ8" s="2"/>
     </row>
